--- a/data/xlsx/bpi--electrical-works-in-energy-sector.xlsx
+++ b/data/xlsx/bpi--electrical-works-in-energy-sector.xlsx
@@ -647,7 +647,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -669,7 +671,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -691,7 +695,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -713,7 +719,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -735,7 +743,9 @@
       <c r="C20" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -757,7 +767,9 @@
       <c r="C21" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -779,7 +791,9 @@
       <c r="C22" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -805,7 +819,9 @@
       <c r="C23" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -827,7 +843,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>8</v>
       </c>
@@ -853,7 +871,9 @@
       <c r="C25" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -879,7 +899,9 @@
       <c r="C26" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -901,7 +923,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>7</v>
       </c>
@@ -923,7 +947,9 @@
       <c r="C28" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>7</v>
       </c>
@@ -945,7 +971,9 @@
       <c r="C29" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>
@@ -967,7 +995,9 @@
       <c r="C30" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>3</v>
       </c>
@@ -993,7 +1023,9 @@
       <c r="C31" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -1015,7 +1047,9 @@
       <c r="C32" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>4</v>
       </c>
@@ -1037,7 +1071,9 @@
       <c r="C33" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>3</v>
       </c>
@@ -1059,7 +1095,9 @@
       <c r="C34" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>3</v>
       </c>
@@ -1081,7 +1119,9 @@
       <c r="C35" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>3</v>
       </c>
@@ -1103,7 +1143,9 @@
       <c r="C36" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>3</v>
       </c>
@@ -1125,7 +1167,9 @@
       <c r="C37" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>4</v>
       </c>
@@ -1147,7 +1191,9 @@
       <c r="C38" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>4</v>
       </c>
@@ -1169,7 +1215,9 @@
       <c r="C39" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>4</v>
       </c>
@@ -1191,7 +1239,9 @@
       <c r="C40" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>6</v>
       </c>
@@ -1213,7 +1263,9 @@
       <c r="C41" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="9" t="n">
         <v>3</v>
       </c>
@@ -1235,7 +1287,9 @@
       <c r="C42" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D42" s="9" t="n"/>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="9" t="n">
         <v>4</v>
       </c>
@@ -1257,7 +1311,9 @@
       <c r="C43" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D43" s="9" t="n"/>
+      <c r="D43" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" s="9" t="n">
         <v>6</v>
       </c>
@@ -1279,7 +1335,9 @@
       <c r="C44" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D44" s="9" t="n"/>
+      <c r="D44" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" s="9" t="n">
         <v>6</v>
       </c>
@@ -1301,7 +1359,9 @@
       <c r="C45" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D45" s="9" t="n"/>
+      <c r="D45" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E45" s="9" t="n">
         <v>5</v>
       </c>
@@ -1323,7 +1383,9 @@
       <c r="C46" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D46" s="9" t="n"/>
+      <c r="D46" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E46" s="9" t="n">
         <v>7</v>
       </c>
@@ -1345,7 +1407,9 @@
       <c r="C47" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D47" s="9" t="n"/>
+      <c r="D47" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E47" s="9" t="n">
         <v>7</v>
       </c>
@@ -1367,7 +1431,9 @@
       <c r="C48" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D48" s="9" t="n"/>
+      <c r="D48" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E48" s="9" t="n">
         <v>5</v>
       </c>
@@ -1389,7 +1455,9 @@
       <c r="C49" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D49" s="9" t="n"/>
+      <c r="D49" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E49" s="9" t="n">
         <v>4</v>
       </c>
@@ -1411,7 +1479,9 @@
       <c r="C50" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D50" s="9" t="n"/>
+      <c r="D50" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E50" s="9" t="n">
         <v>4</v>
       </c>
@@ -1433,7 +1503,9 @@
       <c r="C51" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D51" s="9" t="n"/>
+      <c r="D51" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E51" s="9" t="n">
         <v>4</v>
       </c>
@@ -1455,7 +1527,9 @@
       <c r="C52" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D52" s="9" t="n"/>
+      <c r="D52" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E52" s="9" t="n">
         <v>7</v>
       </c>
@@ -1477,7 +1551,9 @@
       <c r="C53" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D53" s="9" t="n"/>
+      <c r="D53" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E53" s="9" t="n">
         <v>6</v>
       </c>
@@ -1499,7 +1575,9 @@
       <c r="C54" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D54" s="9" t="n"/>
+      <c r="D54" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E54" s="9" t="n">
         <v>3</v>
       </c>
